--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3265-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3265-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5ECA40A3-9280-455C-AB56-3C2E8E8C2039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8C851A8-7DA0-4E7C-ACA6-AB60AB3E4DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{ED929E7C-E34F-4F31-8A08-288D3D427848}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{3BDB833F-BF66-4555-AFB4-6D70BFDC27F8}"/>
   </bookViews>
   <sheets>
     <sheet name="3265-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1460,25 +1460,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E1F59FE-7BB8-47F6-8D9C-6ADBC3448D27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930A4207-7C9A-4106-B200-D46869DD79B0}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1506,7 +1506,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1536,7 +1536,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1632,7 +1632,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="40">
         <v>2024</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="38">
         <v>2023</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2022</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>25</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>25</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2021</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <v>2020</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>25</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>25</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="38">
         <v>2019</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <v>2018</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2017</v>
       </c>
@@ -2622,7 +2622,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>2016</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="38">
         <v>2015</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>2014</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="38">
         <v>2013</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>2012</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="38">
         <v>2011</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>6.53</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="40">
         <v>2010</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="38">
         <v>2009</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2008</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2007</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2006</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38">
         <v>2005</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2004</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2003</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40" t="s">
         <v>38</v>
       </c>
